--- a/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_esenzione_qualsiasi.xlsx
+++ b/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_esenzione_qualsiasi.xlsx
@@ -416,22 +416,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>964</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>949</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>971</t>
         </is>
       </c>
     </row>
@@ -443,22 +443,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.110 (50,3%)</t>
+          <t>1.439 (49,9%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>346 (47,6%)</t>
+          <t>484 (50,2%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>386 (50,5%)</t>
+          <t>469 (49,4%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>378 (52,7%)</t>
+          <t>486 (50,1%)</t>
         </is>
       </c>
     </row>
@@ -470,22 +470,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>727 (32,9%)</t>
+          <t>956 (33,1%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>268 (36,9%)</t>
+          <t>309 (32,1%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>233 (30,5%)</t>
+          <t>323 (34,0%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>226 (31,5%)</t>
+          <t>324 (33,4%)</t>
         </is>
       </c>
     </row>
@@ -497,22 +497,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>737 (33,4%)</t>
+          <t>987 (34,2%)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>207 (28,5%)</t>
+          <t>329 (34,1%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>281 (36,8%)</t>
+          <t>320 (33,7%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>249 (34,7%)</t>
+          <t>338 (34,8%)</t>
         </is>
       </c>
     </row>
@@ -524,22 +524,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>744 (33,7%)</t>
+          <t>941 (32,6%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>252 (34,7%)</t>
+          <t>326 (33,8%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>250 (32,7%)</t>
+          <t>306 (32,2%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>242 (33,8%)</t>
+          <t>309 (31,8%)</t>
         </is>
       </c>
     </row>
@@ -551,22 +551,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>165 (7,5%)</t>
+          <t>1.928 (66,9%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>51 (7,0%)</t>
+          <t>644 (66,8%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>55 (7,2%)</t>
+          <t>634 (66,8%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>59 (8,2%)</t>
+          <t>650 (66,9%)</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A10BH 821 (37,2%)</t>
+          <t>A10BD09 192 (6,7%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A10BH 296 (40,7%)</t>
+          <t>C10BD20 73 (7,6%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A10BK 297 (38,9%)</t>
+          <t>J10JE56 78 (8,2%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A10BJ 275 (38,4%)</t>
+          <t>J10JE54 75 (7,7%)</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A10BD21 804 (36,4%)</t>
+          <t>B10AE54 190 (6,6%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A10BD21 270 (37,1%)</t>
+          <t>M10BD23 69 (7,2%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A10BD15 297 (38,9%)</t>
+          <t>C10BD21 73 (7,7%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A10BD20 270 (37,7%)</t>
+          <t>A10BH02 75 (7,7%)</t>
         </is>
       </c>
     </row>
@@ -639,22 +639,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A10BD15 791 (35,8%)</t>
+          <t>M10BD16 190 (6,6%)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A10BD16 268 (36,9%)</t>
+          <t>C10BD19 68 (7,1%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A10BD07 291 (38,1%)</t>
+          <t>A10AE54 67 (7,1%)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A10BD21 266 (37,1%)</t>
+          <t>M10BD16 71 (7,3%)</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A10AE54 789 (35,7%)</t>
+          <t>J10JE54 188 (6,5%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A10BD07 264 (36,3%)</t>
+          <t>D10BD21 67 (7,0%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A10AE54 286 (37,4%)</t>
+          <t>C10BH02 67 (7,1%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A10BD13 265 (37,0%)</t>
+          <t>D10BD13 70 (7,2%)</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A10BD16 785 (35,6%)</t>
+          <t>B10BD15 184 (6,4%)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A10BD13 257 (35,4%)</t>
+          <t>A10BD19 67 (7,0%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A10BD09 285 (37,3%)</t>
+          <t>D10BJ01 66 (7,0%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A10BD16 259 (36,1%)</t>
+          <t>B10BD21 70 (7,2%)</t>
         </is>
       </c>
     </row>
@@ -727,22 +727,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A10BD 2.193 (99,3%)</t>
+          <t>A10BD B10BD C10BD J10BD M10BD 13 (0,5%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A10BD 720 (99,0%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD 4 (0,4%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A10BD 763 (99,9%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD M10BD 5 (0,5%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A10BD 710 (99,0%)</t>
+          <t>A10BD B10BD C10BD J10BD M10BD 6 (0,6%)</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A10AE 1.089 (49,3%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD M10BD 10 (0,3%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A10AE 360 (49,5%)</t>
+          <t>A10BD B10BD C10BD J10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A10AE 380 (49,7%)</t>
+          <t>A10BD B10BD C10BD J10BD M10BD 4 (0,4%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A10AE 349 (48,7%)</t>
+          <t>A10BD B10BD D10BD J10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A10BH 678 (30,7%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD 9 (0,3%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A10BH 235 (32,3%)</t>
+          <t>A10BD B10BD C10BD D10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A10BK 253 (33,1%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 4 (0,4%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A10BJ 226 (31,5%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A10BK 653 (29,6%)</t>
+          <t>A10BD B10BD C10BD D10BD M10BD 7 (0,2%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A10BX 201 (27,6%)</t>
+          <t>A10BD B10BD D10BD D10DE J10BD M10BD 3 (0,3%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A10BH 229 (30,0%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD 4 (0,4%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A10BH 214 (29,8%)</t>
+          <t>A10AE A10BD B10BD C10BD D10BD J10BD M10BD 2 (0,2%)</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A10BJ 639 (28,9%)</t>
+          <t>A10BD B10BD D10BD J10BD M10BD 6 (0,2%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A10BK 201 (27,6%)</t>
+          <t>A10BD B10BD C10BD D10BD J10BD M10BD M10ME 2 (0,2%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A10BJ 223 (29,2%)</t>
+          <t>A10BD B10BD J10BD J10BK M10BD 2 (0,2%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A10BK 199 (27,8%)</t>
+          <t>A10BD B10BD C10BD D10BD M10BD 2 (0,2%)</t>
         </is>
       </c>
     </row>

--- a/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_esenzione_qualsiasi.xlsx
+++ b/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_esenzione_qualsiasi.xlsx
@@ -585,22 +585,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A10BD09 192 (6,7%)</t>
+          <t>mm 192 (6,7%)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C10BD20 73 (7,6%)</t>
+          <t>NA 73 (7,6%)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>J10JE56 78 (8,2%)</t>
+          <t>NA 78 (8,2%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>J10JE54 75 (7,7%)</t>
+          <t>NA 75 (7,7%)</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B10AE54 190 (6,6%)</t>
+          <t>NA 190 (6,6%)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M10BD23 69 (7,2%)</t>
+          <t>NA 69 (7,2%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C10BD21 73 (7,7%)</t>
+          <t>NA 73 (7,7%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A10BH02 75 (7,7%)</t>
+          <t>NA 75 (7,7%)</t>
         </is>
       </c>
     </row>
@@ -639,22 +639,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M10BD16 190 (6,6%)</t>
+          <t>NA 190 (6,6%)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C10BD19 68 (7,1%)</t>
+          <t>NA 68 (7,1%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A10AE54 67 (7,1%)</t>
+          <t>oo 67 (7,1%)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>M10BD16 71 (7,3%)</t>
+          <t>NA 71 (7,3%)</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J10JE54 188 (6,5%)</t>
+          <t>NA 188 (6,5%)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D10BD21 67 (7,0%)</t>
+          <t>NA 67 (7,0%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C10BH02 67 (7,1%)</t>
+          <t>NA 67 (7,1%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>D10BD13 70 (7,2%)</t>
+          <t>NA 70 (7,2%)</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B10BD15 184 (6,4%)</t>
+          <t>NA 184 (6,4%)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A10BD19 67 (7,0%)</t>
+          <t>gg 67 (7,0%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>D10BJ01 66 (7,0%)</t>
+          <t>NA 66 (7,0%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B10BD21 70 (7,2%)</t>
+          <t>NA 70 (7,2%)</t>
         </is>
       </c>
     </row>
@@ -727,22 +727,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD M10BD 13 (0,5%)</t>
+          <t>e B10BD C10BD D10BD M10BD 186 (3,7%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD 4 (0,4%)</t>
+          <t>e B10BD C10BD D10BD M10BD 62 (3,7%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD M10BD 5 (0,5%)</t>
+          <t>e B10BD C10BD D10BD M10BD 66 (4,1%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD M10BD 6 (0,6%)</t>
+          <t>e B10BD C10BD J10BD M10BD 71 (4,2%)</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD M10BD 10 (0,3%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 178 (3,6%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD M10BD 3 (0,3%)</t>
+          <t>e B10BD C10BD D10BD J10BD 54 (3,2%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD J10BD M10BD 4 (0,4%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 62 (3,8%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A10BD B10BD D10BD J10BD M10BD 3 (0,3%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 65 (3,8%)</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD 9 (0,3%)</t>
+          <t>e B10BD C10BD J10BD M10BD 175 (3,5%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD M10BD 3 (0,3%)</t>
+          <t>e B10BD C10BD J10BD M10BD 52 (3,1%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 4 (0,4%)</t>
+          <t>e B10BD C10BD D10BD J10BD 57 (3,5%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD M10BD 3 (0,3%)</t>
+          <t>e B10BD C10BD D10BD J10BD 62 (3,7%)</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD M10BD 7 (0,2%)</t>
+          <t>e B10BD C10BD D10BD J10BD 173 (3,5%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A10BD B10BD D10BD D10DE J10BD M10BD 3 (0,3%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 51 (3,0%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD 4 (0,4%)</t>
+          <t>e C10BD D10BD J10BD M10BD 55 (3,4%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A10AE A10BD B10BD C10BD D10BD J10BD M10BD 2 (0,2%)</t>
+          <t>e B10BD D10BD J10BD M10BD 59 (3,5%)</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A10BD B10BD D10BD J10BD M10BD 6 (0,2%)</t>
+          <t>e B10BD D10BD J10BD M10BD 162 (3,2%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD J10BD M10BD M10ME 2 (0,2%)</t>
+          <t>e B10BD D10BD J10BD M10BD 50 (3,0%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A10BD B10BD J10BD J10BK M10BD 2 (0,2%)</t>
+          <t>e B10BD D10BD J10BD M10BD 53 (3,3%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A10BD B10BD C10BD D10BD M10BD 2 (0,2%)</t>
+          <t>e B10BD C10BD D10BD M10BD 58 (3,4%)</t>
         </is>
       </c>
     </row>

--- a/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_esenzione_qualsiasi.xlsx
+++ b/i_test/test_D6_Tabella_4_esenzione_2025/g_output/D6_Table_4_esenzione_qualsiasi.xlsx
@@ -727,22 +727,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 186 (3,7%)</t>
+          <t>e B10BD C10BD J10BD M10BD 117 (4,1%)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 62 (3,7%)</t>
+          <t>e B10BD C10BD D10BD M10BD 35 (3,6%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 66 (4,1%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 37 (3,9%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>e B10BD C10BD J10BD M10BD 71 (4,2%)</t>
+          <t>e B10BD C10BD J10BD M10BD 46 (4,7%)</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 178 (3,6%)</t>
+          <t>e B10BD D10BD J10BD M10BD 110 (3,8%)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 54 (3,2%)</t>
+          <t>e B10BD C10BD J10BD M10BD 35 (3,6%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 62 (3,8%)</t>
+          <t>e B10BD C10BD J10BD M10BD 36 (3,8%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 65 (3,8%)</t>
+          <t>e B10BD D10BD J10BD M10BD 43 (4,4%)</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD J10BD M10BD 175 (3,5%)</t>
+          <t>e B10BD C10BD D10BD M10BD 107 (3,7%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD J10BD M10BD 52 (3,1%)</t>
+          <t>e B10BD D10BD J10BD M10BD 34 (3,5%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 57 (3,5%)</t>
+          <t>e B10BD C10BD D10BD M10BD 35 (3,7%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 62 (3,7%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 39 (4,0%)</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD J10BD 173 (3,5%)</t>
+          <t>B10BD C10BD D10BD J10BD M10BD 103 (3,6%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B10BD C10BD D10BD J10BD M10BD 51 (3,0%)</t>
+          <t>e B10BD C10BD D10BD J10BD 33 (3,4%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>e C10BD D10BD J10BD M10BD 55 (3,4%)</t>
+          <t>e B10BD D10BD J10BD M10BD 33 (3,5%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 59 (3,5%)</t>
+          <t>e B10BD C10BD D10BD M10BD 37 (3,8%)</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 162 (3,2%)</t>
+          <t>e B10BD C10BD D10BD J10BD 99 (3,4%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 50 (3,0%)</t>
+          <t>e C10BD D10BD J10BD M10BD 29 (3,0%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>e B10BD D10BD J10BD M10BD 53 (3,3%)</t>
+          <t>e B10BD C10BD D10BD J10BD 32 (3,4%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>e B10BD C10BD D10BD M10BD 58 (3,4%)</t>
+          <t>e B10BD C10BD D10BD J10BD 34 (3,5%)</t>
         </is>
       </c>
     </row>
